--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8064,6 +8064,116 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128330387</v>
+      </c>
+      <c r="B69" t="n">
+        <v>109300</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>695829</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6362190</v>
+      </c>
+      <c r="S69" t="n">
+        <v>50</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>västraallaRobin Karlsson</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Via Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8069,7 +8069,7 @@
         <v>128330387</v>
       </c>
       <c r="B69" t="n">
-        <v>109300</v>
+        <v>109305</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8069,7 +8069,7 @@
         <v>128330387</v>
       </c>
       <c r="B69" t="n">
-        <v>109305</v>
+        <v>109398</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8069,7 +8069,7 @@
         <v>128330387</v>
       </c>
       <c r="B69" t="n">
-        <v>109398</v>
+        <v>109422</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8069,7 +8069,7 @@
         <v>128330387</v>
       </c>
       <c r="B69" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8069,7 +8069,7 @@
         <v>128330387</v>
       </c>
       <c r="B69" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8069,7 +8069,7 @@
         <v>128330387</v>
       </c>
       <c r="B69" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8069,7 +8069,7 @@
         <v>128330387</v>
       </c>
       <c r="B69" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8069,7 +8069,7 @@
         <v>128330387</v>
       </c>
       <c r="B69" t="n">
-        <v>109477</v>
+        <v>109490</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8069,7 +8069,7 @@
         <v>128330387</v>
       </c>
       <c r="B69" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8179,7 +8179,7 @@
         <v>129056284</v>
       </c>
       <c r="B70" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8179,7 +8179,7 @@
         <v>129056284</v>
       </c>
       <c r="B70" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8179,7 +8179,7 @@
         <v>129056284</v>
       </c>
       <c r="B70" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8179,7 +8179,7 @@
         <v>129056284</v>
       </c>
       <c r="B70" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8179,7 +8179,7 @@
         <v>129056284</v>
       </c>
       <c r="B70" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8179,7 +8179,7 @@
         <v>129056284</v>
       </c>
       <c r="B70" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8179,7 +8179,7 @@
         <v>129056284</v>
       </c>
       <c r="B70" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8179,7 +8179,7 @@
         <v>129056284</v>
       </c>
       <c r="B70" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8179,7 +8179,7 @@
         <v>129056284</v>
       </c>
       <c r="B70" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -8179,7 +8179,7 @@
         <v>129056284</v>
       </c>
       <c r="B70" t="n">
-        <v>86967</v>
+        <v>86968</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 2222-2024 artfynd.xlsx
+++ b/artfynd/A 2222-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY120"/>
+  <dimension ref="A1:AZ120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16869376</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104129758</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104129774</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282752</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282753</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282756</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380398</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1489,6 +1529,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380399</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509975</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509976</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1792,6 +1847,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509977</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1898,6 +1958,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16869377</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1999,6 +2064,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330843</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2097,6 +2167,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330882</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2198,6 +2273,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380432</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2299,6 +2379,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380433</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2396,6 +2481,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96691863</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2502,6 +2592,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16869378</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2599,6 +2694,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662080</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2696,6 +2796,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662089</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662109</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2891,6 +3001,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104129746</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2996,6 +3111,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142302</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3097,6 +3217,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282712</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3198,6 +3323,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282713</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3296,6 +3426,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330808</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3394,6 +3529,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330883</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3495,6 +3635,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380366</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3596,6 +3741,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380367</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3697,6 +3847,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509875</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3798,6 +3953,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509876</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3899,6 +4059,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509877</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3998,6 +4163,11 @@
       <c r="AY34" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509878</t>
         </is>
       </c>
     </row>
@@ -4105,6 +4275,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142320</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4206,6 +4381,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282761</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4307,6 +4487,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282762</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4408,6 +4593,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282763</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4509,6 +4699,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282764</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4607,6 +4802,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330788</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4708,6 +4908,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380464</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4809,6 +5014,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380465</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4910,6 +5120,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509992</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5011,6 +5226,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509993</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5108,6 +5328,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129056284</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5216,6 +5441,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104129779</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5317,6 +5547,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282729</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5418,6 +5653,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282732</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5516,6 +5756,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330787</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5614,6 +5859,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330923</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5715,6 +5965,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380457</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5816,6 +6071,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380458</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5917,6 +6177,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380459</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6018,6 +6283,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509929</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6119,6 +6389,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509930</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6220,6 +6495,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729806</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6321,6 +6601,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282727</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6419,6 +6704,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330888</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6516,6 +6806,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662095</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6621,6 +6916,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142307</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6722,6 +7022,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282725</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6821,6 +7126,11 @@
       <c r="AY62" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112729696</t>
         </is>
       </c>
     </row>
@@ -6928,6 +7238,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142308</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7029,6 +7344,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380440</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7127,6 +7447,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534905</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7224,6 +7549,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662100</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7321,6 +7651,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662121</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7422,6 +7757,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791832</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7524,6 +7864,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549079</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7634,6 +7979,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128330387</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7735,6 +8085,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791836</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7836,6 +8191,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112791837</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7938,6 +8298,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549080</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8040,6 +8405,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114549078</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8141,6 +8511,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282736</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8242,6 +8617,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380385</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8343,6 +8723,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509942</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8441,6 +8826,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96648438</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8538,6 +8928,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96662122</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8643,6 +9038,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142310</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8744,6 +9144,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282741</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8845,6 +9250,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282742</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8946,6 +9356,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282743</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9047,6 +9462,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282744</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9148,6 +9568,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282745</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9249,6 +9674,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282746</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9350,6 +9780,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380424</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9451,6 +9886,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380425</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9552,6 +9992,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380426</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9653,6 +10098,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380427</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9754,6 +10204,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509956</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9855,6 +10310,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509957</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9956,6 +10416,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509958</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10057,6 +10522,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509959</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10158,6 +10628,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509960</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10259,6 +10734,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509961</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10360,6 +10840,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509962</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10461,6 +10946,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509963</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10561,6 +11051,11 @@
       <c r="AY99" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509964</t>
         </is>
       </c>
     </row>
@@ -10668,6 +11163,11 @@
           <t>Sveriges Mykologiska Förenings kursverksamhet</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104142304</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10769,6 +11269,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282715</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10870,6 +11375,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282717</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10971,6 +11481,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282719</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11072,6 +11587,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282720</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11173,6 +11693,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282721</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11274,6 +11799,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282722</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11372,6 +11902,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330791</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11470,6 +12005,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330897</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11568,6 +12108,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104330905</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11669,6 +12214,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380407</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11770,6 +12320,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380408</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11871,6 +12426,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509904</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11972,6 +12532,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509905</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12073,6 +12638,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509906</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12174,6 +12744,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509907</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12275,6 +12850,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509909</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12376,6 +12956,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104509910</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12477,6 +13062,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282733</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12578,6 +13168,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104282734</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12675,8 +13270,134 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104380402</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>